--- a/EBS pollock/Data/BSP0.xlsx
+++ b/EBS pollock/Data/BSP0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\grant.adams\GitHub\Rceattle-models\EBS pollock\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51F730F5-6200-465D-92F5-2A26C300454B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CA7C08B-D5A1-4ED9-8BA4-D54736673035}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1008" windowWidth="34560" windowHeight="21108" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1005" windowWidth="34560" windowHeight="21105" firstSheet="2" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="catch_data" sheetId="5" r:id="rId1"/>
@@ -23,7 +23,7 @@
     <sheet name="NByageFixed" sheetId="8" r:id="rId8"/>
     <sheet name="age_trans_matrix" sheetId="9" r:id="rId9"/>
     <sheet name="age_error" sheetId="10" r:id="rId10"/>
-    <sheet name="wt" sheetId="11" r:id="rId11"/>
+    <sheet name="weight" sheetId="11" r:id="rId11"/>
     <sheet name="pmature" sheetId="12" r:id="rId12"/>
     <sheet name="sex_ratio" sheetId="13" r:id="rId13"/>
     <sheet name="M1_base" sheetId="14" r:id="rId14"/>
@@ -1296,7 +1296,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:H62"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
@@ -2918,7 +2918,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:Q16"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:17" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
@@ -3776,9 +3776,9 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:T306"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" s="1" customFormat="1">
@@ -22761,7 +22761,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:P2"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
@@ -22871,7 +22871,7 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:P2"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
@@ -22981,7 +22981,7 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:Q2"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:17" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
@@ -23097,7 +23097,7 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
@@ -23129,7 +23129,7 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
@@ -23243,7 +23243,7 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:B43"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
@@ -23597,7 +23597,7 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:R2"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:18" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
@@ -23719,7 +23719,7 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1:I101"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
@@ -26658,10 +26658,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G47"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="4" max="4" width="169.6640625" customWidth="1"/>
-    <col min="5" max="5" width="17.109375" customWidth="1"/>
+    <col min="4" max="4" width="169.7109375" customWidth="1"/>
+    <col min="5" max="5" width="17.140625" customWidth="1"/>
     <col min="6" max="6" width="22" customWidth="1"/>
   </cols>
   <sheetData>
@@ -27565,9 +27565,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B19"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="22.109375" customWidth="1"/>
+    <col min="1" max="1" width="22.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1">
@@ -27721,20 +27721,20 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AB7"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="5" max="5" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.85546875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17.88671875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -28300,9 +28300,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:I158"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="1" customFormat="1">
@@ -32813,7 +32813,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:W122"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:23" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
@@ -41485,7 +41485,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:T186"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:20" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
@@ -53027,7 +53027,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:AH62"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:34" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
@@ -56740,7 +56740,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:AD16"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:30" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
